--- a/workbooks/high-confidence-recovery.xlsx
+++ b/workbooks/high-confidence-recovery.xlsx
@@ -5,20 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Anil\1. Power BI\Fabric\new_SaaS\final\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Anil\GitHub\newbridge-saas-operating-system\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C048A92B-BA97-49C1-992D-B074C248C1AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5F1A79C-034D-46F2-8B21-CA1B31923F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19470" windowHeight="15585" activeTab="1" xr2:uid="{E93CEB74-9002-4B77-A4DA-58E626EA608A}"/>
+    <workbookView xWindow="75" yWindow="0" windowWidth="20370" windowHeight="15480" activeTab="1" xr2:uid="{E93CEB74-9002-4B77-A4DA-58E626EA608A}"/>
   </bookViews>
   <sheets>
     <sheet name="LP-Scenario8" sheetId="1" r:id="rId1"/>
     <sheet name="LP-Scenario9A" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="solver_adj" localSheetId="0" hidden="1">'LP-Scenario8'!$B$20:$D$27</definedName>
-    <definedName name="solver_adj" localSheetId="1" hidden="1">'LP-Scenario9A'!$B$20:$D$27</definedName>
     <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="1" hidden="1">0.0001</definedName>
     <definedName name="solver_drv" localSheetId="0" hidden="1">1</definedName>
@@ -29,30 +27,30 @@
     <definedName name="solver_est" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="1" hidden="1">2147483647</definedName>
-    <definedName name="solver_lhs1" localSheetId="0" hidden="1">'LP-Scenario8'!$B$46</definedName>
-    <definedName name="solver_lhs1" localSheetId="1" hidden="1">'LP-Scenario9A'!$B$46</definedName>
-    <definedName name="solver_lhs10" localSheetId="0" hidden="1">'LP-Scenario8'!$B$55</definedName>
-    <definedName name="solver_lhs10" localSheetId="1" hidden="1">'LP-Scenario9A'!$B$55</definedName>
-    <definedName name="solver_lhs11" localSheetId="0" hidden="1">'LP-Scenario8'!$B$56</definedName>
-    <definedName name="solver_lhs11" localSheetId="1" hidden="1">'LP-Scenario9A'!$B$56</definedName>
+    <definedName name="solver_lhs1" localSheetId="0" hidden="1">'LP-Scenario8'!$B$57</definedName>
+    <definedName name="solver_lhs1" localSheetId="1" hidden="1">'LP-Scenario9A'!$B$51</definedName>
+    <definedName name="solver_lhs10" localSheetId="0" hidden="1">'LP-Scenario8'!$B$57</definedName>
+    <definedName name="solver_lhs10" localSheetId="1" hidden="1">'LP-Scenario9A'!$B$57</definedName>
+    <definedName name="solver_lhs11" localSheetId="0" hidden="1">'LP-Scenario8'!$B$57</definedName>
+    <definedName name="solver_lhs11" localSheetId="1" hidden="1">'LP-Scenario9A'!$B$57</definedName>
     <definedName name="solver_lhs12" localSheetId="0" hidden="1">'LP-Scenario8'!$B$57</definedName>
     <definedName name="solver_lhs12" localSheetId="1" hidden="1">'LP-Scenario9A'!$B$57</definedName>
-    <definedName name="solver_lhs2" localSheetId="0" hidden="1">'LP-Scenario8'!$B$47</definedName>
-    <definedName name="solver_lhs2" localSheetId="1" hidden="1">'LP-Scenario9A'!$B$47</definedName>
-    <definedName name="solver_lhs3" localSheetId="0" hidden="1">'LP-Scenario8'!$B$48</definedName>
-    <definedName name="solver_lhs3" localSheetId="1" hidden="1">'LP-Scenario9A'!$B$48</definedName>
-    <definedName name="solver_lhs4" localSheetId="0" hidden="1">'LP-Scenario8'!$B$49</definedName>
-    <definedName name="solver_lhs4" localSheetId="1" hidden="1">'LP-Scenario9A'!$B$49</definedName>
-    <definedName name="solver_lhs5" localSheetId="0" hidden="1">'LP-Scenario8'!$B$50</definedName>
-    <definedName name="solver_lhs5" localSheetId="1" hidden="1">'LP-Scenario9A'!$B$50</definedName>
-    <definedName name="solver_lhs6" localSheetId="0" hidden="1">'LP-Scenario8'!$B$51</definedName>
-    <definedName name="solver_lhs6" localSheetId="1" hidden="1">'LP-Scenario9A'!$B$51</definedName>
-    <definedName name="solver_lhs7" localSheetId="0" hidden="1">'LP-Scenario8'!$B$52</definedName>
-    <definedName name="solver_lhs7" localSheetId="1" hidden="1">'LP-Scenario9A'!$B$52</definedName>
-    <definedName name="solver_lhs8" localSheetId="0" hidden="1">'LP-Scenario8'!$B$53</definedName>
-    <definedName name="solver_lhs8" localSheetId="1" hidden="1">'LP-Scenario9A'!$B$53</definedName>
-    <definedName name="solver_lhs9" localSheetId="0" hidden="1">'LP-Scenario8'!$B$54</definedName>
-    <definedName name="solver_lhs9" localSheetId="1" hidden="1">'LP-Scenario9A'!$B$54</definedName>
+    <definedName name="solver_lhs2" localSheetId="0" hidden="1">'LP-Scenario8'!$B$53</definedName>
+    <definedName name="solver_lhs2" localSheetId="1" hidden="1">'LP-Scenario9A'!$B$53</definedName>
+    <definedName name="solver_lhs3" localSheetId="0" hidden="1">'LP-Scenario8'!$B$54</definedName>
+    <definedName name="solver_lhs3" localSheetId="1" hidden="1">'LP-Scenario9A'!$B$54</definedName>
+    <definedName name="solver_lhs4" localSheetId="0" hidden="1">'LP-Scenario8'!$B$55</definedName>
+    <definedName name="solver_lhs4" localSheetId="1" hidden="1">'LP-Scenario9A'!$B$57</definedName>
+    <definedName name="solver_lhs5" localSheetId="0" hidden="1">'LP-Scenario8'!$B$56</definedName>
+    <definedName name="solver_lhs5" localSheetId="1" hidden="1">'LP-Scenario9A'!$B$57</definedName>
+    <definedName name="solver_lhs6" localSheetId="0" hidden="1">'LP-Scenario8'!$B$57</definedName>
+    <definedName name="solver_lhs6" localSheetId="1" hidden="1">'LP-Scenario9A'!$B$57</definedName>
+    <definedName name="solver_lhs7" localSheetId="0" hidden="1">'LP-Scenario8'!$B$57</definedName>
+    <definedName name="solver_lhs7" localSheetId="1" hidden="1">'LP-Scenario9A'!$B$57</definedName>
+    <definedName name="solver_lhs8" localSheetId="0" hidden="1">'LP-Scenario8'!$B$57</definedName>
+    <definedName name="solver_lhs8" localSheetId="1" hidden="1">'LP-Scenario9A'!$B$57</definedName>
+    <definedName name="solver_lhs9" localSheetId="0" hidden="1">'LP-Scenario8'!$B$57</definedName>
+    <definedName name="solver_lhs9" localSheetId="1" hidden="1">'LP-Scenario9A'!$B$57</definedName>
     <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
@@ -65,12 +63,10 @@
     <definedName name="solver_neg" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="1" hidden="1">2147483647</definedName>
-    <definedName name="solver_num" localSheetId="0" hidden="1">12</definedName>
-    <definedName name="solver_num" localSheetId="1" hidden="1">12</definedName>
+    <definedName name="solver_num" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_num" localSheetId="1" hidden="1">0</definedName>
     <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="1" hidden="1">1</definedName>
-    <definedName name="solver_opt" localSheetId="0" hidden="1">'LP-Scenario8'!$E$41</definedName>
-    <definedName name="solver_opt" localSheetId="1" hidden="1">'LP-Scenario9A'!$E$41</definedName>
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="1" hidden="1">0.000001</definedName>
     <definedName name="solver_rbv" localSheetId="0" hidden="1">1</definedName>
@@ -99,30 +95,30 @@
     <definedName name="solver_rel8" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_rel9" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel9" localSheetId="1" hidden="1">1</definedName>
-    <definedName name="solver_rhs1" localSheetId="0" hidden="1">'LP-Scenario8'!$C$46</definedName>
-    <definedName name="solver_rhs1" localSheetId="1" hidden="1">'LP-Scenario9A'!$C$46</definedName>
-    <definedName name="solver_rhs10" localSheetId="0" hidden="1">'LP-Scenario8'!$C$55</definedName>
-    <definedName name="solver_rhs10" localSheetId="1" hidden="1">'LP-Scenario9A'!$C$55</definedName>
-    <definedName name="solver_rhs11" localSheetId="0" hidden="1">'LP-Scenario8'!$C$56</definedName>
-    <definedName name="solver_rhs11" localSheetId="1" hidden="1">'LP-Scenario9A'!$C$56</definedName>
+    <definedName name="solver_rhs1" localSheetId="0" hidden="1">'LP-Scenario8'!$C$57</definedName>
+    <definedName name="solver_rhs1" localSheetId="1" hidden="1">'LP-Scenario9A'!$C$51</definedName>
+    <definedName name="solver_rhs10" localSheetId="0" hidden="1">'LP-Scenario8'!$C$57</definedName>
+    <definedName name="solver_rhs10" localSheetId="1" hidden="1">'LP-Scenario9A'!$C$57</definedName>
+    <definedName name="solver_rhs11" localSheetId="0" hidden="1">'LP-Scenario8'!$C$57</definedName>
+    <definedName name="solver_rhs11" localSheetId="1" hidden="1">'LP-Scenario9A'!$C$57</definedName>
     <definedName name="solver_rhs12" localSheetId="0" hidden="1">'LP-Scenario8'!$C$57</definedName>
     <definedName name="solver_rhs12" localSheetId="1" hidden="1">'LP-Scenario9A'!$C$57</definedName>
-    <definedName name="solver_rhs2" localSheetId="0" hidden="1">'LP-Scenario8'!$C$47</definedName>
-    <definedName name="solver_rhs2" localSheetId="1" hidden="1">'LP-Scenario9A'!$C$47</definedName>
-    <definedName name="solver_rhs3" localSheetId="0" hidden="1">'LP-Scenario8'!$C$48</definedName>
-    <definedName name="solver_rhs3" localSheetId="1" hidden="1">'LP-Scenario9A'!$C$48</definedName>
-    <definedName name="solver_rhs4" localSheetId="0" hidden="1">'LP-Scenario8'!$C$49</definedName>
-    <definedName name="solver_rhs4" localSheetId="1" hidden="1">'LP-Scenario9A'!$C$49</definedName>
-    <definedName name="solver_rhs5" localSheetId="0" hidden="1">'LP-Scenario8'!$C$50</definedName>
-    <definedName name="solver_rhs5" localSheetId="1" hidden="1">'LP-Scenario9A'!$C$50</definedName>
-    <definedName name="solver_rhs6" localSheetId="0" hidden="1">'LP-Scenario8'!$C$51</definedName>
-    <definedName name="solver_rhs6" localSheetId="1" hidden="1">'LP-Scenario9A'!$C$51</definedName>
-    <definedName name="solver_rhs7" localSheetId="0" hidden="1">'LP-Scenario8'!$C$52</definedName>
-    <definedName name="solver_rhs7" localSheetId="1" hidden="1">'LP-Scenario9A'!$C$52</definedName>
-    <definedName name="solver_rhs8" localSheetId="0" hidden="1">'LP-Scenario8'!$C$53</definedName>
-    <definedName name="solver_rhs8" localSheetId="1" hidden="1">'LP-Scenario9A'!$C$53</definedName>
-    <definedName name="solver_rhs9" localSheetId="0" hidden="1">'LP-Scenario8'!$C$54</definedName>
-    <definedName name="solver_rhs9" localSheetId="1" hidden="1">'LP-Scenario9A'!$C$54</definedName>
+    <definedName name="solver_rhs2" localSheetId="0" hidden="1">'LP-Scenario8'!$C$53</definedName>
+    <definedName name="solver_rhs2" localSheetId="1" hidden="1">'LP-Scenario9A'!$C$53</definedName>
+    <definedName name="solver_rhs3" localSheetId="0" hidden="1">'LP-Scenario8'!$C$54</definedName>
+    <definedName name="solver_rhs3" localSheetId="1" hidden="1">'LP-Scenario9A'!$C$54</definedName>
+    <definedName name="solver_rhs4" localSheetId="0" hidden="1">'LP-Scenario8'!$C$55</definedName>
+    <definedName name="solver_rhs4" localSheetId="1" hidden="1">'LP-Scenario9A'!$C$57</definedName>
+    <definedName name="solver_rhs5" localSheetId="0" hidden="1">'LP-Scenario8'!$C$56</definedName>
+    <definedName name="solver_rhs5" localSheetId="1" hidden="1">'LP-Scenario9A'!$C$57</definedName>
+    <definedName name="solver_rhs6" localSheetId="0" hidden="1">'LP-Scenario8'!$C$57</definedName>
+    <definedName name="solver_rhs6" localSheetId="1" hidden="1">'LP-Scenario9A'!$C$57</definedName>
+    <definedName name="solver_rhs7" localSheetId="0" hidden="1">'LP-Scenario8'!$C$57</definedName>
+    <definedName name="solver_rhs7" localSheetId="1" hidden="1">'LP-Scenario9A'!$C$57</definedName>
+    <definedName name="solver_rhs8" localSheetId="0" hidden="1">'LP-Scenario8'!$C$57</definedName>
+    <definedName name="solver_rhs8" localSheetId="1" hidden="1">'LP-Scenario9A'!$C$57</definedName>
+    <definedName name="solver_rhs9" localSheetId="0" hidden="1">'LP-Scenario8'!$C$57</definedName>
+    <definedName name="solver_rhs9" localSheetId="1" hidden="1">'LP-Scenario9A'!$C$57</definedName>
     <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
